--- a/data/a_Eingangsdaten/Optimierungsgrößen - Copy - Copy (2).xlsx
+++ b/data/a_Eingangsdaten/Optimierungsgrößen - Copy - Copy (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\a_Eingangsdaten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDE6C81-5EF0-4C4C-BD2F-AC8D5E64989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B238F72B-013F-40D5-A6CB-B5E0467605AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>999</v>
+        <v>99999999</v>
       </c>
       <c r="F14">
         <v>9999</v>
@@ -1022,6 +1022,9 @@
       </c>
       <c r="I17">
         <v>304300000</v>
+      </c>
+      <c r="J17">
+        <v>1E-3</v>
       </c>
       <c r="K17">
         <v>0.1</v>
